--- a/exports/trend_1d/TITAN_full_report.xlsx
+++ b/exports/trend_1d/TITAN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.77</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42082</v>
+        <v>42083</v>
       </c>
       <c r="H2" t="n">
-        <v>404.8</v>
+        <v>392.7</v>
       </c>
       <c r="I2" t="n">
         <v>396.2686601562698</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K2" t="n">
-        <v>7.69</v>
+        <v>4.47</v>
       </c>
       <c r="L2" t="n">
         <v>1.65</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.99</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42242</v>
+        <v>42243</v>
       </c>
       <c r="H3" t="n">
-        <v>324.75</v>
+        <v>347.05</v>
       </c>
       <c r="I3" t="n">
         <v>345.4692676235488</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K3" t="n">
-        <v>17.3</v>
+        <v>11.62</v>
       </c>
       <c r="L3" t="n">
         <v>7.61</v>
@@ -612,7 +647,7 @@
         <v>1.53</v>
       </c>
       <c r="N3" t="n">
-        <v>3.97</v>
+        <v>6.87</v>
       </c>
       <c r="O3" t="n">
         <v>-2.99</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.62</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42361</v>
+        <v>42362</v>
       </c>
       <c r="H4" t="n">
-        <v>358.2</v>
+        <v>350.65</v>
       </c>
       <c r="I4" t="n">
         <v>351.8347768398914</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K4" t="n">
-        <v>3.21</v>
+        <v>1.04</v>
       </c>
       <c r="L4" t="n">
         <v>12.76</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.93</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42404</v>
+        <v>42405</v>
       </c>
       <c r="H5" t="n">
-        <v>362</v>
+        <v>369.55</v>
       </c>
       <c r="I5" t="n">
         <v>364.8202085141419</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.24</v>
+        <v>-5.39</v>
       </c>
       <c r="L5" t="n">
         <v>6.35</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>11.1</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42416</v>
+        <v>42417</v>
       </c>
       <c r="H6" t="n">
-        <v>347.55</v>
+        <v>326.85</v>
       </c>
       <c r="I6" t="n">
         <v>333.7538270939153</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.95</v>
+        <v>-11.55</v>
       </c>
       <c r="L6" t="n">
-        <v>7.7</v>
+        <v>12.58</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.79</v>
+        <v>5.96</v>
       </c>
       <c r="O6" t="n">
         <v>2.09</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>15.92</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42473</v>
+        <v>42478</v>
       </c>
       <c r="H7" t="n">
-        <v>352.85</v>
+        <v>361.8</v>
       </c>
       <c r="I7" t="n">
         <v>360.3528884038186</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.95</v>
+        <v>-10.69</v>
       </c>
       <c r="L7" t="n">
-        <v>10.45</v>
+        <v>11.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.48</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.1</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42606</v>
+        <v>42607</v>
       </c>
       <c r="H8" t="n">
-        <v>404.15</v>
+        <v>395.1</v>
       </c>
       <c r="I8" t="n">
         <v>395.6891584737744</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K8" t="n">
-        <v>11.71</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>3.52</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42615</v>
+        <v>42619</v>
       </c>
       <c r="H9" t="n">
-        <v>418.35</v>
+        <v>437.45</v>
       </c>
       <c r="I9" t="n">
         <v>433.4414735577254</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.88</v>
+        <v>-10.72</v>
       </c>
       <c r="L9" t="n">
-        <v>7.37</v>
+        <v>11.36</v>
       </c>
       <c r="M9" t="n">
         <v>0.84</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>4.57</v>
       </c>
       <c r="O9" t="n">
         <v>-2.24</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>9.76</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H10" t="n">
-        <v>409.7</v>
+        <v>393.15</v>
       </c>
       <c r="I10" t="n">
         <v>396.2632787058171</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.34</v>
+        <v>-10.13</v>
       </c>
       <c r="L10" t="n">
-        <v>8.630000000000001</v>
+        <v>10.61</v>
       </c>
       <c r="M10" t="n">
         <v>0.93</v>
       </c>
       <c r="N10" t="n">
-        <v>2.98</v>
+        <v>4.04</v>
       </c>
       <c r="O10" t="n">
         <v>4.57</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>11.01</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="H11" t="n">
-        <v>333.95</v>
+        <v>348.15</v>
       </c>
       <c r="I11" t="n">
         <v>342.4899879131554</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K11" t="n">
-        <v>15.06</v>
+        <v>11.45</v>
       </c>
       <c r="L11" t="n">
         <v>5.29</v>
       </c>
       <c r="M11" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="N11" t="n">
-        <v>4.04</v>
+        <v>4.25</v>
       </c>
       <c r="O11" t="n">
         <v>-4.04</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.77</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43003</v>
+        <v>43004</v>
       </c>
       <c r="H12" t="n">
-        <v>602.15</v>
+        <v>592.25</v>
       </c>
       <c r="I12" t="n">
         <v>601.9188246946665</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K12" t="n">
-        <v>72.95999999999999</v>
+        <v>70.11</v>
       </c>
       <c r="L12" t="n">
         <v>2.59</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43038</v>
+        <v>43039</v>
       </c>
       <c r="H13" t="n">
-        <v>618.3</v>
+        <v>635.25</v>
       </c>
       <c r="I13" t="n">
         <v>630.1455292967079</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.4</v>
+        <v>-7.26</v>
       </c>
       <c r="L13" t="n">
-        <v>6.96</v>
+        <v>7.98</v>
       </c>
       <c r="M13" t="n">
         <v>3.92</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.94</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43131</v>
+        <v>43132</v>
       </c>
       <c r="H14" t="n">
-        <v>869.55</v>
+        <v>831</v>
       </c>
       <c r="I14" t="n">
         <v>862.5801215017538</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K14" t="n">
-        <v>36.88</v>
+        <v>30.81</v>
       </c>
       <c r="L14" t="n">
         <v>2.2</v>
@@ -1239,7 +1406,7 @@
         <v>3.78</v>
       </c>
       <c r="N14" t="n">
-        <v>3.82</v>
+        <v>4.43</v>
       </c>
       <c r="O14" t="n">
         <v>2.74</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>12.41</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43174</v>
+        <v>43175</v>
       </c>
       <c r="H15" t="n">
-        <v>872.5</v>
+        <v>879.25</v>
       </c>
       <c r="I15" t="n">
         <v>872.6835298309526</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.99</v>
+        <v>-5.81</v>
       </c>
       <c r="L15" t="n">
-        <v>5.79</v>
+        <v>6.31</v>
       </c>
       <c r="M15" t="n">
         <v>1.11</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.53</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43238</v>
+        <v>43241</v>
       </c>
       <c r="H16" t="n">
-        <v>939.95</v>
+        <v>915.25</v>
       </c>
       <c r="I16" t="n">
         <v>918.7585884703122</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K16" t="n">
-        <v>6.9</v>
+        <v>4.09</v>
       </c>
       <c r="L16" t="n">
         <v>2.18</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43308</v>
+        <v>43311</v>
       </c>
       <c r="H17" t="n">
-        <v>884.1</v>
+        <v>892.05</v>
       </c>
       <c r="I17" t="n">
         <v>890.9234831516941</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4</v>
+        <v>2.53</v>
       </c>
       <c r="L17" t="n">
         <v>3.2</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H18" t="n">
-        <v>880.9</v>
+        <v>863.9</v>
       </c>
       <c r="I18" t="n">
         <v>864.9250616252436</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.25</v>
+        <v>-3.16</v>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>4.53</v>
       </c>
       <c r="M18" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="N18" t="n">
         <v>3.49</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43413</v>
+        <v>43416</v>
       </c>
       <c r="H19" t="n">
-        <v>847.65</v>
+        <v>894.75</v>
       </c>
       <c r="I19" t="n">
         <v>872.947801309273</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K19" t="n">
-        <v>1.88</v>
+        <v>-3.57</v>
       </c>
       <c r="L19" t="n">
-        <v>2.33</v>
+        <v>4.35</v>
       </c>
       <c r="M19" t="n">
         <v>2.32</v>
       </c>
       <c r="N19" t="n">
-        <v>5.21</v>
+        <v>5.56</v>
       </c>
       <c r="O19" t="n">
         <v>-1.93</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>12.91</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H20" t="n">
-        <v>1278.1</v>
+        <v>1252.45</v>
       </c>
       <c r="I20" t="n">
         <v>1256.251308154654</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="K20" t="n">
-        <v>42.84</v>
+        <v>39.98</v>
       </c>
       <c r="L20" t="n">
         <v>5.76</v>
       </c>
       <c r="M20" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="N20" t="n">
         <v>5.43</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>161</v>
+        <v>162</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.33</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43721</v>
+        <v>43724</v>
       </c>
       <c r="H21" t="n">
-        <v>1123.4</v>
+        <v>1148.55</v>
       </c>
       <c r="I21" t="n">
         <v>1126.617938189578</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K21" t="n">
-        <v>10.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>1.47</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>9.66</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43774</v>
+        <v>43775</v>
       </c>
       <c r="H22" t="n">
-        <v>1283.8</v>
+        <v>1156.1</v>
       </c>
       <c r="I22" t="n">
         <v>1259.68742895483</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K22" t="n">
-        <v>11.78</v>
+        <v>0.66</v>
       </c>
       <c r="L22" t="n">
         <v>2.89</v>
       </c>
       <c r="M22" t="n">
-        <v>4.69</v>
+        <v>9.25</v>
       </c>
       <c r="N22" t="n">
-        <v>3.44</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O22" t="n">
         <v>2.24</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>13.24</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43853</v>
+        <v>43854</v>
       </c>
       <c r="H23" t="n">
-        <v>1204.1</v>
+        <v>1227.85</v>
       </c>
       <c r="I23" t="n">
         <v>1214.762188129293</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.15</v>
+        <v>-6.21</v>
       </c>
       <c r="L23" t="n">
-        <v>6.31</v>
+        <v>6.39</v>
       </c>
       <c r="M23" t="n">
         <v>1.96</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.15</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43889</v>
+        <v>43892</v>
       </c>
       <c r="H24" t="n">
-        <v>1254.5</v>
+        <v>1244.15</v>
       </c>
       <c r="I24" t="n">
         <v>1246.730569741632</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K24" t="n">
-        <v>2.17</v>
+        <v>1.33</v>
       </c>
       <c r="L24" t="n">
         <v>5.32</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H25" t="n">
-        <v>890</v>
+        <v>958.9</v>
       </c>
       <c r="I25" t="n">
         <v>940.7026994622584</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K25" t="n">
-        <v>28.47</v>
+        <v>22.93</v>
       </c>
       <c r="L25" t="n">
         <v>4.01</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.9</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44097</v>
+        <v>44098</v>
       </c>
       <c r="H26" t="n">
-        <v>1117.2</v>
+        <v>1096.15</v>
       </c>
       <c r="I26" t="n">
         <v>1096.39532239062</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K26" t="n">
-        <v>16.51</v>
+        <v>14.31</v>
       </c>
       <c r="L26" t="n">
         <v>6.3</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44103</v>
+        <v>44104</v>
       </c>
       <c r="H27" t="n">
-        <v>1167.3</v>
+        <v>1201.35</v>
       </c>
       <c r="I27" t="n">
         <v>1197.110162783566</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.49</v>
+        <v>-9.6</v>
       </c>
       <c r="L27" t="n">
-        <v>7.12</v>
+        <v>9.93</v>
       </c>
       <c r="M27" t="n">
         <v>0.87</v>
       </c>
       <c r="N27" t="n">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="O27" t="n">
         <v>-1.88</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.19</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44210</v>
+        <v>44211</v>
       </c>
       <c r="H28" t="n">
-        <v>1489.95</v>
+        <v>1477.25</v>
       </c>
       <c r="I28" t="n">
         <v>1482.01071345613</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K28" t="n">
-        <v>24.02</v>
+        <v>22.97</v>
       </c>
       <c r="L28" t="n">
         <v>3.94</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44235</v>
+        <v>44236</v>
       </c>
       <c r="H29" t="n">
-        <v>1541.7</v>
+        <v>1559.9</v>
       </c>
       <c r="I29" t="n">
         <v>1554.23879862243</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.36</v>
+        <v>-5.59</v>
       </c>
       <c r="L29" t="n">
-        <v>5.93</v>
+        <v>7.27</v>
       </c>
       <c r="M29" t="n">
         <v>1.23</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>8.65</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44246</v>
+        <v>44249</v>
       </c>
       <c r="H30" t="n">
-        <v>1425.55</v>
+        <v>1405.25</v>
       </c>
       <c r="I30" t="n">
         <v>1425.022055638751</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K30" t="n">
-        <v>-8.609999999999999</v>
+        <v>-9.91</v>
       </c>
       <c r="L30" t="n">
-        <v>9.43</v>
+        <v>10.51</v>
       </c>
       <c r="M30" t="n">
         <v>0.71</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>10.05</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44281</v>
+        <v>44285</v>
       </c>
       <c r="H31" t="n">
-        <v>1505.85</v>
+        <v>1552.2</v>
       </c>
       <c r="I31" t="n">
         <v>1542.45558809411</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.16</v>
+        <v>-10.46</v>
       </c>
       <c r="L31" t="n">
-        <v>8.949999999999999</v>
+        <v>11.23</v>
       </c>
       <c r="M31" t="n">
         <v>1.16</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>9</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44316</v>
+        <v>44319</v>
       </c>
       <c r="H32" t="n">
-        <v>1491.65</v>
+        <v>1423.95</v>
       </c>
       <c r="I32" t="n">
         <v>1451.159922903303</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.9</v>
+        <v>-8.26</v>
       </c>
       <c r="L32" t="n">
-        <v>6.48</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M32" t="n">
         <v>1.55</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>11.05</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44340</v>
+        <v>44341</v>
       </c>
       <c r="H33" t="n">
-        <v>1520.75</v>
+        <v>1569.15</v>
       </c>
       <c r="I33" t="n">
         <v>1542.710777163029</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.8</v>
+        <v>-10.2</v>
       </c>
       <c r="L33" t="n">
-        <v>9.99</v>
+        <v>10.6</v>
       </c>
       <c r="M33" t="n">
         <v>1.36</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H34" t="n">
-        <v>1680.35</v>
+        <v>1671.4</v>
       </c>
       <c r="I34" t="n">
         <v>1674.974720207166</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K34" t="n">
-        <v>7.09</v>
+        <v>6.52</v>
       </c>
       <c r="L34" t="n">
         <v>2.18</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>5.55</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44407</v>
+        <v>44410</v>
       </c>
       <c r="H35" t="n">
-        <v>1714.55</v>
+        <v>1771.55</v>
       </c>
       <c r="I35" t="n">
         <v>1764.168909913036</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.58</v>
+        <v>-5.99</v>
       </c>
       <c r="L35" t="n">
-        <v>5.08</v>
+        <v>6.26</v>
       </c>
       <c r="M35" t="n">
         <v>1.41</v>
       </c>
       <c r="N35" t="n">
-        <v>1.82</v>
+        <v>3.32</v>
       </c>
       <c r="O35" t="n">
         <v>-0.53</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.07</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H36" t="n">
-        <v>2412</v>
+        <v>2379.15</v>
       </c>
       <c r="I36" t="n">
         <v>2384.429193881899</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K36" t="n">
-        <v>36.15</v>
+        <v>34.3</v>
       </c>
       <c r="L36" t="n">
         <v>2.63</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.83</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44559</v>
+        <v>44560</v>
       </c>
       <c r="H37" t="n">
-        <v>2402.15</v>
+        <v>2437.3</v>
       </c>
       <c r="I37" t="n">
         <v>2431.806734425597</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.97</v>
+        <v>-2.44</v>
       </c>
       <c r="L37" t="n">
         <v>8.140000000000001</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>7.65</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H38" t="n">
-        <v>2528.15</v>
+        <v>2403.05</v>
       </c>
       <c r="I38" t="n">
         <v>2458.529385752716</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K38" t="n">
-        <v>3.73</v>
+        <v>-1.41</v>
       </c>
       <c r="L38" t="n">
-        <v>1.91</v>
+        <v>2.52</v>
       </c>
       <c r="M38" t="n">
         <v>1.4</v>
       </c>
       <c r="N38" t="n">
-        <v>1.52</v>
+        <v>4.95</v>
       </c>
       <c r="O38" t="n">
         <v>1.46</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>10.42</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44617</v>
+        <v>44620</v>
       </c>
       <c r="H39" t="n">
-        <v>2468.45</v>
+        <v>2546.55</v>
       </c>
       <c r="I39" t="n">
         <v>2531.503012527546</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.72</v>
+        <v>-5.97</v>
       </c>
       <c r="L39" t="n">
-        <v>5.59</v>
+        <v>6.68</v>
       </c>
       <c r="M39" t="n">
         <v>1.62</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.28</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44657</v>
+        <v>44658</v>
       </c>
       <c r="H40" t="n">
-        <v>2540.05</v>
+        <v>2458.35</v>
       </c>
       <c r="I40" t="n">
         <v>2498.20825248844</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.26</v>
+        <v>-3.46</v>
       </c>
       <c r="L40" t="n">
         <v>8.68</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>9.65</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H41" t="n">
-        <v>2013.55</v>
+        <v>2127.5</v>
       </c>
       <c r="I41" t="n">
         <v>2108.309589539223</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K41" t="n">
-        <v>18.09</v>
+        <v>13.46</v>
       </c>
       <c r="L41" t="n">
         <v>3.82</v>
       </c>
       <c r="M41" t="n">
-        <v>1.78</v>
+        <v>5.78</v>
       </c>
       <c r="N41" t="n">
         <v>5.93</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.54</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44881</v>
+        <v>44882</v>
       </c>
       <c r="H42" t="n">
-        <v>2644.3</v>
+        <v>2582</v>
       </c>
       <c r="I42" t="n">
         <v>2597.877024750301</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K42" t="n">
-        <v>24.29</v>
+        <v>21.36</v>
       </c>
       <c r="L42" t="n">
         <v>1.17</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.74</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44959</v>
+        <v>44960</v>
       </c>
       <c r="H43" t="n">
-        <v>2308.1</v>
+        <v>2463.1</v>
       </c>
       <c r="I43" t="n">
         <v>2456.205547923823</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K43" t="n">
-        <v>10.61</v>
+        <v>4.6</v>
       </c>
       <c r="L43" t="n">
         <v>3.21</v>
@@ -2892,7 +3407,7 @@
         <v>1.32</v>
       </c>
       <c r="N43" t="n">
-        <v>3.06</v>
+        <v>6.72</v>
       </c>
       <c r="O43" t="n">
         <v>-2.36</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.3</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44984</v>
+        <v>44985</v>
       </c>
       <c r="H44" t="n">
-        <v>2401</v>
+        <v>2372.8</v>
       </c>
       <c r="I44" t="n">
         <v>2382.435486283184</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.52</v>
+        <v>-3.67</v>
       </c>
       <c r="L44" t="n">
         <v>5.81</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>6.93</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45005</v>
+        <v>45006</v>
       </c>
       <c r="H45" t="n">
-        <v>2459.95</v>
+        <v>2514.05</v>
       </c>
       <c r="I45" t="n">
         <v>2481.318944713972</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.67</v>
+        <v>-5.95</v>
       </c>
       <c r="L45" t="n">
-        <v>4.6</v>
+        <v>6.27</v>
       </c>
       <c r="M45" t="n">
         <v>1.04</v>
       </c>
       <c r="N45" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="O45" t="n">
         <v>-1.17</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.54</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45124</v>
+        <v>45125</v>
       </c>
       <c r="H46" t="n">
-        <v>3033.45</v>
+        <v>2996.45</v>
       </c>
       <c r="I46" t="n">
         <v>3019.037757584693</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K46" t="n">
-        <v>20.66</v>
+        <v>19.19</v>
       </c>
       <c r="L46" t="n">
         <v>1.88</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>5.72</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="H47" t="n">
-        <v>3011.1</v>
+        <v>3071.75</v>
       </c>
       <c r="I47" t="n">
         <v>3058.721571058737</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.49</v>
+        <v>-2.51</v>
       </c>
       <c r="L47" t="n">
-        <v>2.37</v>
+        <v>2.77</v>
       </c>
       <c r="M47" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="O47" t="n">
         <v>-1.22</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.07</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45196</v>
+        <v>45197</v>
       </c>
       <c r="H48" t="n">
-        <v>3214.55</v>
+        <v>3157.25</v>
       </c>
       <c r="I48" t="n">
         <v>3168.727090860452</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K48" t="n">
-        <v>4.65</v>
+        <v>2.78</v>
       </c>
       <c r="L48" t="n">
         <v>1.95</v>
@@ -3177,7 +3752,7 @@
         <v>0.76</v>
       </c>
       <c r="N48" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="O48" t="n">
         <v>2.01</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.18</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="H49" t="n">
-        <v>3201.5</v>
+        <v>3274.5</v>
       </c>
       <c r="I49" t="n">
         <v>3266.66022128654</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.4</v>
+        <v>-3.71</v>
       </c>
       <c r="L49" t="n">
         <v>5.44</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.59</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="H50" t="n">
-        <v>3697.55</v>
+        <v>3627.45</v>
       </c>
       <c r="I50" t="n">
         <v>3641.27053995505</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K50" t="n">
-        <v>12.92</v>
+        <v>10.78</v>
       </c>
       <c r="L50" t="n">
         <v>2.12</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="H51" t="n">
-        <v>3750.75</v>
+        <v>3810.75</v>
       </c>
       <c r="I51" t="n">
         <v>3797.613658618291</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.4</v>
+        <v>-5.05</v>
       </c>
       <c r="L51" t="n">
-        <v>4.15</v>
+        <v>5.17</v>
       </c>
       <c r="M51" t="n">
         <v>1.09</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>7.46</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45398</v>
+        <v>45400</v>
       </c>
       <c r="H52" t="n">
-        <v>3645.9</v>
+        <v>3525.1</v>
       </c>
       <c r="I52" t="n">
         <v>3570.179237026795</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.33</v>
+        <v>-7.5</v>
       </c>
       <c r="L52" t="n">
-        <v>6.92</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M52" t="n">
         <v>1.12</v>
       </c>
       <c r="N52" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="O52" t="n">
         <v>1.6</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.65</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45449</v>
+        <v>45450</v>
       </c>
       <c r="H53" t="n">
-        <v>3321.65</v>
+        <v>3444.05</v>
       </c>
       <c r="I53" t="n">
         <v>3443.559761343278</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K53" t="n">
-        <v>5.77</v>
+        <v>2.3</v>
       </c>
       <c r="L53" t="n">
         <v>3.83</v>
@@ -3462,7 +4097,7 @@
         <v>2.1</v>
       </c>
       <c r="N53" t="n">
-        <v>2.43</v>
+        <v>3.68</v>
       </c>
       <c r="O53" t="n">
         <v>-3.31</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>10.56</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45477</v>
+        <v>45478</v>
       </c>
       <c r="H54" t="n">
-        <v>3336</v>
+        <v>3269.35</v>
       </c>
       <c r="I54" t="n">
         <v>3327.519716814139</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.14</v>
+        <v>-5.07</v>
       </c>
       <c r="L54" t="n">
-        <v>4.35</v>
+        <v>5.43</v>
       </c>
       <c r="M54" t="n">
         <v>0.82</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>6.98</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45495</v>
+        <v>45496</v>
       </c>
       <c r="H55" t="n">
-        <v>3254.45</v>
+        <v>3466.85</v>
       </c>
       <c r="I55" t="n">
         <v>3390.800606376017</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K55" t="n">
-        <v>0.46</v>
+        <v>-6.04</v>
       </c>
       <c r="L55" t="n">
-        <v>1.92</v>
+        <v>6.75</v>
       </c>
       <c r="M55" t="n">
         <v>0.68</v>
       </c>
       <c r="N55" t="n">
-        <v>1.87</v>
+        <v>6.53</v>
       </c>
       <c r="O55" t="n">
         <v>-2</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H56" t="n">
-        <v>3670.1</v>
+        <v>3589.25</v>
       </c>
       <c r="I56" t="n">
         <v>3609.341466235233</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K56" t="n">
-        <v>5.86</v>
+        <v>3.53</v>
       </c>
       <c r="L56" t="n">
         <v>6.77</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.81</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45630</v>
+        <v>45631</v>
       </c>
       <c r="H57" t="n">
-        <v>3364.45</v>
+        <v>3441.05</v>
       </c>
       <c r="I57" t="n">
         <v>3395.566214649443</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K57" t="n">
-        <v>6.26</v>
+        <v>4.13</v>
       </c>
       <c r="L57" t="n">
         <v>4.42</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>7.74</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="H58" t="n">
-        <v>3309.2</v>
+        <v>3257.35</v>
       </c>
       <c r="I58" t="n">
         <v>3265.32316280923</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.83</v>
+        <v>-5.34</v>
       </c>
       <c r="L58" t="n">
-        <v>4.07</v>
+        <v>5.63</v>
       </c>
       <c r="M58" t="n">
         <v>1.54</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>7.09</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="H59" t="n">
-        <v>3388.95</v>
+        <v>3451.65</v>
       </c>
       <c r="I59" t="n">
         <v>3443.49560864802</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.04</v>
+        <v>-5.96</v>
       </c>
       <c r="L59" t="n">
-        <v>4.41</v>
+        <v>6.9</v>
       </c>
       <c r="M59" t="n">
         <v>0.31</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>7.08</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45698</v>
+        <v>45699</v>
       </c>
       <c r="H60" t="n">
-        <v>3327.45</v>
+        <v>3281.8</v>
       </c>
       <c r="I60" t="n">
         <v>3308.550188680675</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.6</v>
+        <v>-4.92</v>
       </c>
       <c r="L60" t="n">
-        <v>4.92</v>
+        <v>5.22</v>
       </c>
       <c r="M60" t="n">
         <v>1.75</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.94</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45756</v>
+        <v>45758</v>
       </c>
       <c r="H61" t="n">
-        <v>3174.15</v>
+        <v>3234.9</v>
       </c>
       <c r="I61" t="n">
         <v>3205.946630349621</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K61" t="n">
-        <v>3.28</v>
+        <v>1.43</v>
       </c>
       <c r="L61" t="n">
         <v>2.02</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="H62" t="n">
-        <v>3666.1</v>
+        <v>3441.3</v>
       </c>
       <c r="I62" t="n">
         <v>3520.978998421054</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K62" t="n">
-        <v>13.33</v>
+        <v>6.38</v>
       </c>
       <c r="L62" t="n">
         <v>1.04</v>
       </c>
       <c r="M62" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="N62" t="n">
-        <v>2.51</v>
+        <v>6.13</v>
       </c>
       <c r="O62" t="n">
         <v>1.91</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>8.44</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45880</v>
+        <v>45881</v>
       </c>
       <c r="H63" t="n">
-        <v>3467.9</v>
+        <v>3486.8</v>
       </c>
       <c r="I63" t="n">
         <v>3485.513973688222</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.77</v>
+        <v>-1.32</v>
       </c>
       <c r="L63" t="n">
         <v>4.08</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.24</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="H64" t="n">
-        <v>3556.8</v>
+        <v>3523</v>
       </c>
       <c r="I64" t="n">
         <v>3523.345904577233</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K64" t="n">
-        <v>2.01</v>
+        <v>1.04</v>
       </c>
       <c r="L64" t="n">
         <v>0.77</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>5.37</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="H65" t="n">
-        <v>3418.2</v>
+        <v>3565.6</v>
       </c>
       <c r="I65" t="n">
         <v>3519.90565726251</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K65" t="n">
-        <v>2.97</v>
+        <v>-1.21</v>
       </c>
       <c r="L65" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="M65" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="N65" t="n">
-        <v>2.22</v>
+        <v>4.31</v>
       </c>
       <c r="O65" t="n">
         <v>-0.95</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>7.4</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="H66" t="n">
-        <v>4079.2</v>
+        <v>4018.6</v>
       </c>
       <c r="I66" t="n">
         <v>4059.732765234874</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K66" t="n">
-        <v>14.4</v>
+        <v>12.7</v>
       </c>
       <c r="L66" t="n">
         <v>2.96</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>6.85</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H67" t="n">
-        <v>4141</v>
+        <v>4257.8</v>
       </c>
       <c r="I67" t="n">
         <v>4157.974878850792</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.05</v>
+        <v>-5.95</v>
       </c>
       <c r="L67" t="n">
-        <v>3.52</v>
+        <v>6.24</v>
       </c>
       <c r="M67" t="n">
         <v>4.8</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="H68" t="n">
-        <v>4129.6</v>
+        <v>4073.2</v>
       </c>
       <c r="I68" t="n">
         <v>4106.957215493327</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.01</v>
+        <v>-4.34</v>
       </c>
       <c r="L68" t="n">
         <v>5.26</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>8.08</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H69" t="n">
-        <v>4230.6</v>
+        <v>4492.5</v>
       </c>
       <c r="I69" t="n">
         <v>4285.703243798584</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.86</v>
+        <v>-10.29</v>
       </c>
       <c r="L69" t="n">
-        <v>4.53</v>
+        <v>10.6</v>
       </c>
       <c r="M69" t="n">
-        <v>2.52</v>
+        <v>2.85</v>
       </c>
       <c r="N69" t="n">
-        <v>3.63</v>
+        <v>6.19</v>
       </c>
       <c r="O69" t="n">
         <v>-1.37</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>11.32</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H70" t="n">
-        <v>4205.6</v>
+        <v>4055.3</v>
       </c>
       <c r="I70" t="n">
         <v>4136.35051020038</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K70" t="n">
-        <v>-6.39</v>
+        <v>-9.73</v>
       </c>
       <c r="L70" t="n">
-        <v>7.62</v>
+        <v>9.92</v>
       </c>
       <c r="M70" t="n">
         <v>3.52</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>13.25</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="H71" t="n">
-        <v>4283.5</v>
+        <v>4338</v>
       </c>
       <c r="I71" t="n">
         <v>4334.067175648019</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K71" t="n">
-        <v>-5.63</v>
+        <v>-6.97</v>
       </c>
       <c r="L71" t="n">
-        <v>5.96</v>
+        <v>7.12</v>
       </c>
       <c r="M71" t="n">
         <v>1.06</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H72" t="n">
-        <v>5009.5</v>
+        <v>4856</v>
       </c>
       <c r="I72" t="n">
         <v>4928.115137308644</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K72" t="n">
-        <v>15.48</v>
+        <v>11.94</v>
       </c>
       <c r="L72" t="n">
         <v>2.6</v>
@@ -4545,7 +5408,7 @@
         <v>1.96</v>
       </c>
       <c r="N72" t="n">
-        <v>1.54</v>
+        <v>3.06</v>
       </c>
       <c r="O72" t="n">
         <v>1.27</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>30</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9563,7 +10446,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -9573,7 +10456,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -9583,7 +10466,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8">
@@ -9593,7 +10476,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9603,7 +10486,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79.5</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="10">
@@ -9613,7 +10496,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -9653,7 +10536,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.35</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="15">
@@ -9663,7 +10546,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.56</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="16">
@@ -9673,7 +10556,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.02</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="17">
@@ -9683,7 +10566,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>72.95999999999999</v>
+        <v>70.11</v>
       </c>
     </row>
     <row r="18">
@@ -9693,7 +10576,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.7</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="19">
@@ -9703,7 +10586,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.74</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="20">
@@ -9713,7 +10596,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.41</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="21">
@@ -9733,7 +10616,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -9743,7 +10626,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -9753,7 +10636,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="25">
@@ -9763,7 +10646,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.8</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="26">
@@ -9773,7 +10656,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.61</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="27">
@@ -9793,7 +10676,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
